--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118031088</v>
+        <v>118031532</v>
       </c>
       <c r="B2" t="n">
-        <v>79069</v>
+        <v>78125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710283</v>
+        <v>710193</v>
       </c>
       <c r="R2" t="n">
-        <v>7419517</v>
+        <v>7419637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118031532</v>
+        <v>118031088</v>
       </c>
       <c r="B3" t="n">
-        <v>78125</v>
+        <v>79069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710193</v>
+        <v>710283</v>
       </c>
       <c r="R3" t="n">
-        <v>7419637</v>
+        <v>7419517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118031591</v>
+        <v>118031041</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>90766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
+          <t>Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710147</v>
+        <v>710329</v>
       </c>
       <c r="R4" t="n">
-        <v>7419618</v>
+        <v>7419521</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118031041</v>
+        <v>118031591</v>
       </c>
       <c r="B5" t="n">
-        <v>90766</v>
+        <v>79098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haikakbäcken, Lu lm</t>
+          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710329</v>
+        <v>710147</v>
       </c>
       <c r="R5" t="n">
-        <v>7419521</v>
+        <v>7419618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118031532</v>
       </c>
       <c r="B2" t="n">
-        <v>78125</v>
+        <v>78127</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118031088</v>
+        <v>118031041</v>
       </c>
       <c r="B3" t="n">
-        <v>79069</v>
+        <v>90768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>71</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
+          <t>Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710283</v>
+        <v>710329</v>
       </c>
       <c r="R3" t="n">
-        <v>7419517</v>
+        <v>7419521</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118031041</v>
+        <v>118031088</v>
       </c>
       <c r="B4" t="n">
-        <v>90766</v>
+        <v>79071</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haikakbäcken, Lu lm</t>
+          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710329</v>
+        <v>710283</v>
       </c>
       <c r="R4" t="n">
-        <v>7419521</v>
+        <v>7419517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>118031591</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118031532</v>
+        <v>118031041</v>
       </c>
       <c r="B2" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
+          <t>Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>710193</v>
+        <v>710329</v>
       </c>
       <c r="R2" t="n">
-        <v>7419637</v>
+        <v>7419521</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118031591</v>
+        <v>118031532</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
+          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710147</v>
+        <v>710193</v>
       </c>
       <c r="R3" t="n">
-        <v>7419618</v>
+        <v>7419637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118031088</v>
+        <v>118031591</v>
       </c>
       <c r="B4" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haikakbäcken (Haikakbäcken), Lu lm</t>
+          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710283</v>
+        <v>710147</v>
       </c>
       <c r="R4" t="n">
-        <v>7419517</v>
+        <v>7419618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118031041</v>
+        <v>118031088</v>
       </c>
       <c r="B5" t="n">
-        <v>90772</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haikakbäcken, Lu lm</t>
+          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710329</v>
+        <v>710283</v>
       </c>
       <c r="R5" t="n">
-        <v>7419521</v>
+        <v>7419517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118031532</v>
+        <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>710193</v>
+        <v>710083</v>
       </c>
       <c r="R3" t="n">
-        <v>7419637</v>
+        <v>7419972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,33 +871,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118031532</t>
+          <t>https://artportalen.se/Sighting/135916615</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118031591</v>
+        <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>79946</v>
+        <v>92000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>710147</v>
+        <v>710038</v>
       </c>
       <c r="R4" t="n">
-        <v>7419618</v>
+        <v>7419927</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +990,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118031591</t>
+          <t>https://artportalen.se/Sighting/135916616</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118031088</v>
+        <v>118031532</v>
       </c>
       <c r="B5" t="n">
-        <v>79917</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>710283</v>
+        <v>710193</v>
       </c>
       <c r="R5" t="n">
-        <v>7419517</v>
+        <v>7419637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,6 +1102,770 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031532</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135916611</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92103</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>710148</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7420019</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135916611</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135916613</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93341</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>710117</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7420011</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135916613</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135916614</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93347</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>710112</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7420013</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135916614</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118031591</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>710147</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7419618</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118031591</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135916609</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>710157</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7419995</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135916609</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135916612</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>710146</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7420012</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135916612</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118031088</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Haikakbäcken, Haikakbäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>710283</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7419517</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/118031088</t>
         </is>
@@ -1092,6 +1877,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32990-2023 artfynd.xlsx
+++ b/artfynd/A 32990-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135916615</v>
       </c>
       <c r="B3" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>135916616</v>
       </c>
       <c r="B4" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>135916611</v>
       </c>
       <c r="B6" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>135916613</v>
       </c>
       <c r="B7" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>135916614</v>
       </c>
       <c r="B8" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>135916609</v>
       </c>
       <c r="B10" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>135916612</v>
       </c>
       <c r="B11" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
